--- a/modeling/report/03-eval-final.xlsx
+++ b/modeling/report/03-eval-final.xlsx
@@ -1404,46 +1404,46 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>289</v>
+        <v>304</v>
       </c>
       <c r="C10" t="n">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="D10" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="E10" t="n">
-        <v>291</v>
+        <v>273</v>
       </c>
       <c r="F10" t="n">
-        <v>208</v>
+        <v>172</v>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>-31</v>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>-31</v>
       </c>
       <c r="I10" t="n">
-        <v>-204</v>
+        <v>-234</v>
       </c>
       <c r="J10" t="n">
-        <v>0.773936170212766</v>
+        <v>0.7959183673469388</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7768817204301075</v>
+        <v>0.7506172839506173</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7780748663101604</v>
+        <v>0.7299465240641712</v>
       </c>
       <c r="M10" t="n">
-        <v>0.7727272727272727</v>
+        <v>0.8128342245989305</v>
       </c>
       <c r="N10" t="n">
-        <v>0.776</v>
+        <v>0.7615062761506276</v>
       </c>
       <c r="O10" t="n">
-        <v>0.774798927613941</v>
+        <v>0.7804878048780488</v>
       </c>
       <c r="P10" t="n">
         <v>374</v>
@@ -1452,46 +1452,46 @@
         <v>374</v>
       </c>
       <c r="R10" t="n">
-        <v>0.7754010695187166</v>
+        <v>0.7713903743315508</v>
       </c>
       <c r="S10" t="n">
         <v>748</v>
       </c>
       <c r="T10" t="n">
-        <v>0.7754089453214368</v>
+        <v>0.7732678256487781</v>
       </c>
       <c r="U10" t="n">
-        <v>0.7754010695187166</v>
+        <v>0.7713903743315509</v>
       </c>
       <c r="V10" t="n">
-        <v>0.7753994638069706</v>
+        <v>0.7709970405143383</v>
       </c>
       <c r="W10" t="n">
         <v>748</v>
       </c>
       <c r="X10" t="n">
-        <v>0.7754089453214367</v>
+        <v>0.7732678256487779</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.7754010695187166</v>
+        <v>0.7713903743315508</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.7753994638069706</v>
+        <v>0.7709970405143383</v>
       </c>
       <c r="AA10" t="n">
         <v>748</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8535774543166805</v>
+        <v>0.8521762132174212</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.7754010695187166</v>
+        <v>0.7713903743315508</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.2245989304812834</v>
+        <v>0.2286096256684492</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.1016042780748663</v>
+        <v>0.08556149732620322</v>
       </c>
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="inlineStr"/>
@@ -1503,46 +1503,46 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>303</v>
+        <v>284</v>
       </c>
       <c r="C11" t="n">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="D11" t="n">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="E11" t="n">
-        <v>262</v>
+        <v>289</v>
       </c>
       <c r="F11" t="n">
-        <v>150</v>
+        <v>204</v>
       </c>
       <c r="G11" t="n">
-        <v>-41</v>
+        <v>5</v>
       </c>
       <c r="H11" t="n">
-        <v>-41</v>
+        <v>5</v>
       </c>
       <c r="I11" t="n">
-        <v>-232</v>
+        <v>-194</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7867867867867868</v>
+        <v>0.762532981530343</v>
       </c>
       <c r="K11" t="n">
-        <v>0.7301204819277108</v>
+        <v>0.7696476964769647</v>
       </c>
       <c r="L11" t="n">
-        <v>0.7005347593582888</v>
+        <v>0.7727272727272727</v>
       </c>
       <c r="M11" t="n">
-        <v>0.8101604278074866</v>
+        <v>0.7593582887700535</v>
       </c>
       <c r="N11" t="n">
-        <v>0.7411598302687411</v>
+        <v>0.7675962815405046</v>
       </c>
       <c r="O11" t="n">
-        <v>0.7680608365019012</v>
+        <v>0.7644683714670256</v>
       </c>
       <c r="P11" t="n">
         <v>374</v>
@@ -1551,46 +1551,46 @@
         <v>374</v>
       </c>
       <c r="R11" t="n">
-        <v>0.7553475935828877</v>
+        <v>0.7660427807486631</v>
       </c>
       <c r="S11" t="n">
         <v>748</v>
       </c>
       <c r="T11" t="n">
-        <v>0.7584536343572488</v>
+        <v>0.7660903390036539</v>
       </c>
       <c r="U11" t="n">
-        <v>0.7553475935828877</v>
+        <v>0.7660427807486632</v>
       </c>
       <c r="V11" t="n">
-        <v>0.7546103333853211</v>
+        <v>0.7660323265037652</v>
       </c>
       <c r="W11" t="n">
         <v>748</v>
       </c>
       <c r="X11" t="n">
-        <v>0.7584536343572488</v>
+        <v>0.7660903390036539</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.7553475935828877</v>
+        <v>0.7660427807486631</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.7546103333853212</v>
+        <v>0.7660323265037652</v>
       </c>
       <c r="AA11" t="n">
         <v>748</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8355471989476393</v>
+        <v>0.8476007320769825</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.7553475935828877</v>
+        <v>0.7660427807486631</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.2446524064171123</v>
+        <v>0.2339572192513369</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.02139037433155078</v>
+        <v>0.06417112299465244</v>
       </c>
       <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="inlineStr"/>
